--- a/Pruebas Unitarias Hipoteca inversa.xlsx
+++ b/Pruebas Unitarias Hipoteca inversa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ccf2a03b9ec56bd6/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4abf091ba1c8ec3f/Documentos/codigo_limpio_bueno/CALCULADORA-DE-HIPOTECA-INVERSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C84CD018-41AB-0E48-97F7-E9005DEB94B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44E82598-F362-48F6-9379-D2E2636E8A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3A6D69DF-D47A-49DD-A42D-8E27133C0724}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3A6D69DF-D47A-49DD-A42D-8E27133C0724}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>CASOS</t>
   </si>
@@ -65,24 +65,9 @@
     <t>Caso normal 2</t>
   </si>
   <si>
-    <t>Tasa de interés</t>
-  </si>
-  <si>
     <t>Valor del inmueble</t>
   </si>
   <si>
-    <t>Porcentaje financiado</t>
-  </si>
-  <si>
-    <t>Plazo estimado</t>
-  </si>
-  <si>
-    <t>Valor de la cuota mensual</t>
-  </si>
-  <si>
-    <t>Total estimado acumulado</t>
-  </si>
-  <si>
     <t>Saldo proyectado de la deuda</t>
   </si>
   <si>
@@ -123,6 +108,24 @@
   </si>
   <si>
     <t>Error: la tasa de interés debe ser mayor a 0.</t>
+  </si>
+  <si>
+    <t>Tasa de capitalizacion</t>
+  </si>
+  <si>
+    <t>Plazo de simulacion</t>
+  </si>
+  <si>
+    <t>Porcentaje LTV permitido</t>
+  </si>
+  <si>
+    <t>Monto mensual recibido</t>
+  </si>
+  <si>
+    <t>Total recibido acumulado</t>
+  </si>
+  <si>
+    <t>Tasa de capita;izacion</t>
   </si>
 </sst>
 </file>
@@ -130,9 +133,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -231,15 +234,15 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -258,14 +261,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -275,34 +274,31 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -657,73 +653,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C096A64-EBD1-4097-8827-79A9BC47E3A7}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.52734375" style="12" customWidth="1"/>
-    <col min="4" max="4" width="11.296875" customWidth="1"/>
-    <col min="5" max="5" width="16.8125" customWidth="1"/>
-    <col min="6" max="6" width="21.7890625" customWidth="1"/>
-    <col min="7" max="7" width="29.7265625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="29.7265625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="27.171875" customWidth="1"/>
+    <col min="1" max="1" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" customWidth="1"/>
+    <col min="7" max="7" width="29.77734375" customWidth="1"/>
+    <col min="8" max="8" width="29.77734375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="27.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30" t="s">
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+    </row>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="2">
         <v>300000000</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="14">
         <v>0.08</v>
       </c>
       <c r="D3" s="1">
@@ -735,7 +731,7 @@
       <c r="F3" s="5">
         <v>0.4</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="15">
         <f>PMT(C3/12,E3*12,-(B3*F3))</f>
         <v>1003728.0827921554</v>
       </c>
@@ -748,14 +744,14 @@
         <v>559314857.26191676</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2">
         <v>450000000</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D4" s="1">
@@ -767,7 +763,7 @@
       <c r="F4" s="5">
         <v>0.35</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="15">
         <f>PMT(C4/12,E4*12,-(B4*F4))</f>
         <v>1113177.2357082695</v>
       </c>
@@ -780,54 +776,54 @@
         <v>854820640.81935537</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="13"/>
+      <c r="C5" s="11"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
+      <c r="G5" s="17"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+    </row>
+    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="24" t="s">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="B7" s="2">
         <v>900000000</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="16">
         <v>7.5499999999999998E-2</v>
       </c>
       <c r="D7" s="1">
@@ -839,27 +835,27 @@
       <c r="F7" s="5">
         <v>0.3</v>
       </c>
-      <c r="G7" s="17">
-        <f t="shared" ref="G5:G12" si="0">PMT(C7/12,E7*12,-(B7*F7))</f>
+      <c r="G7" s="15">
+        <f t="shared" ref="G7:G12" si="0">PMT(C7/12,E7*12,-(B7*F7))</f>
         <v>2510611.0823132163</v>
       </c>
       <c r="H7" s="2">
-        <f t="shared" ref="H5:H12" si="1">G7*E7*12</f>
+        <f t="shared" ref="H7:H12" si="1">G7*E7*12</f>
         <v>451909994.81637895</v>
       </c>
       <c r="I7" s="2">
-        <f t="shared" ref="I5:I12" si="2">B7*F7*(1+C7)^E7</f>
+        <f t="shared" ref="I7:I12" si="2">B7*F7*(1+C7)^E7</f>
         <v>804488768.01195729</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2">
         <v>350000000</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="13">
         <v>0.08</v>
       </c>
       <c r="D8" s="1">
@@ -871,7 +867,7 @@
       <c r="F8" s="5">
         <v>0.45</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="15">
         <f t="shared" si="0"/>
         <v>1155679.2038600175</v>
       </c>
@@ -884,14 +880,14 @@
         <v>1584868460.0290675</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2">
         <v>250000000</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="13">
         <v>0.09</v>
       </c>
       <c r="D9" s="1">
@@ -903,7 +899,7 @@
       <c r="F9" s="5">
         <v>0.7</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="15">
         <f t="shared" si="0"/>
         <v>1574520.4227378028</v>
       </c>
@@ -916,14 +912,14 @@
         <v>980771884.36120212</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2">
         <v>400000000</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="13">
         <v>0.05</v>
       </c>
       <c r="D10" s="1">
@@ -935,7 +931,7 @@
       <c r="F10" s="5">
         <v>0.4</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="15">
         <f t="shared" si="0"/>
         <v>1055929.1827466518</v>
       </c>
@@ -948,14 +944,14 @@
         <v>424527632.82310736</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2">
         <v>280000000</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="13">
         <v>0.08</v>
       </c>
       <c r="D11" s="1">
@@ -967,7 +963,7 @@
       <c r="F11" s="5">
         <v>0.5</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="15">
         <f t="shared" si="0"/>
         <v>1698586.320974997</v>
       </c>
@@ -980,14 +976,14 @@
         <v>302249499.61819029</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2">
         <v>150000000</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="13">
         <v>0.09</v>
       </c>
       <c r="D12" s="1">
@@ -999,7 +995,7 @@
       <c r="F12" s="5">
         <v>0.6</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="15">
         <f t="shared" si="0"/>
         <v>755276.72727135918</v>
       </c>
@@ -1012,54 +1008,54 @@
         <v>776077259.4362874</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="5.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="14"/>
+      <c r="C13" s="12"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="11"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="9"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="21" t="s">
+    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="24" t="s">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="B15" s="2">
         <v>300000000</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13">
         <v>0.08</v>
       </c>
       <c r="D15" s="1">
@@ -1071,20 +1067,20 @@
       <c r="F15" s="5">
         <v>0.4</v>
       </c>
-      <c r="G15" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G15" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B16" s="2">
         <v>350000000</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D16" s="1">
@@ -1096,20 +1092,20 @@
       <c r="F16" s="5">
         <v>1.2</v>
       </c>
-      <c r="G16" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G16" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2">
         <v>280000000</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="24">
         <v>0.08</v>
       </c>
       <c r="D17" s="7">
@@ -1118,21 +1114,21 @@
       <c r="E17" s="7">
         <v>20</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="24">
         <v>-0.3</v>
       </c>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B18" s="2">
         <v>400000000</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="24">
         <v>-0.05</v>
       </c>
       <c r="D18" s="7">
@@ -1141,14 +1137,14 @@
       <c r="E18" s="7">
         <v>20</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="24">
         <v>0.4</v>
       </c>
-      <c r="G18" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
+      <c r="G18" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
